--- a/Data Files/OTM Test Data/OTM Order data.xlsx
+++ b/Data Files/OTM Test Data/OTM Order data.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Order ID</t>
   </si>
@@ -106,6 +106,9 @@
   </si>
   <si>
     <t>SO_TEST965834</t>
+  </si>
+  <si>
+    <t>SO_TEST228797</t>
   </si>
 </sst>
 </file>
@@ -458,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87F71A60-031B-47A6-9564-1B4B3385F003}">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="15.51953125" collapsed="true"/>
@@ -597,6 +600,11 @@
     <row r="27">
       <c r="A27" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/Data Files/OTM Test Data/OTM Order data.xlsx
+++ b/Data Files/OTM Test Data/OTM Order data.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>Order ID</t>
   </si>
@@ -109,6 +109,12 @@
   </si>
   <si>
     <t>SO_TEST228797</t>
+  </si>
+  <si>
+    <t>SO_TEST352103</t>
+  </si>
+  <si>
+    <t>SO_TEST669744</t>
   </si>
 </sst>
 </file>
@@ -461,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87F71A60-031B-47A6-9564-1B4B3385F003}">
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="15.51953125" collapsed="true"/>
@@ -605,6 +611,16 @@
     <row r="28">
       <c r="A28" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Data Files/OTM Test Data/OTM Order data.xlsx
+++ b/Data Files/OTM Test Data/OTM Order data.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Order ID</t>
   </si>
@@ -115,6 +115,9 @@
   </si>
   <si>
     <t>SO_TEST669744</t>
+  </si>
+  <si>
+    <t>SO_TEST298276</t>
   </si>
 </sst>
 </file>
@@ -467,7 +470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87F71A60-031B-47A6-9564-1B4B3385F003}">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="15.51953125" collapsed="true"/>
@@ -621,6 +624,11 @@
     <row r="30">
       <c r="A30" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/Data Files/OTM Test Data/OTM Order data.xlsx
+++ b/Data Files/OTM Test Data/OTM Order data.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Order ID</t>
   </si>
@@ -118,6 +118,9 @@
   </si>
   <si>
     <t>SO_TEST298276</t>
+  </si>
+  <si>
+    <t>SO_TEST104067</t>
   </si>
 </sst>
 </file>
@@ -470,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87F71A60-031B-47A6-9564-1B4B3385F003}">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="15.51953125" collapsed="true"/>
@@ -629,6 +632,11 @@
     <row r="31">
       <c r="A31" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/Data Files/OTM Test Data/OTM Order data.xlsx
+++ b/Data Files/OTM Test Data/OTM Order data.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>Order ID</t>
   </si>
@@ -121,6 +121,12 @@
   </si>
   <si>
     <t>SO_TEST104067</t>
+  </si>
+  <si>
+    <t>SO_TEST195082</t>
+  </si>
+  <si>
+    <t>SO_TEST532262</t>
   </si>
 </sst>
 </file>
@@ -473,7 +479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87F71A60-031B-47A6-9564-1B4B3385F003}">
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="15.51953125" collapsed="true"/>
@@ -637,6 +643,16 @@
     <row r="32">
       <c r="A32" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/Data Files/OTM Test Data/OTM Order data.xlsx
+++ b/Data Files/OTM Test Data/OTM Order data.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>Order ID</t>
   </si>
@@ -127,6 +127,12 @@
   </si>
   <si>
     <t>SO_TEST532262</t>
+  </si>
+  <si>
+    <t>SO_TEST628467</t>
+  </si>
+  <si>
+    <t>SO_TEST251519</t>
   </si>
 </sst>
 </file>
@@ -479,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87F71A60-031B-47A6-9564-1B4B3385F003}">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="15.51953125" collapsed="true"/>
@@ -653,6 +659,16 @@
     <row r="34">
       <c r="A34" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/Data Files/OTM Test Data/OTM Order data.xlsx
+++ b/Data Files/OTM Test Data/OTM Order data.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Order ID</t>
   </si>
@@ -121,6 +121,9 @@
   </si>
   <si>
     <t>SO_TEST104067</t>
+  </si>
+  <si>
+    <t>SO_TEST456240</t>
   </si>
 </sst>
 </file>
@@ -473,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87F71A60-031B-47A6-9564-1B4B3385F003}">
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="15.51953125" collapsed="true"/>
@@ -637,6 +640,11 @@
     <row r="32">
       <c r="A32" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/Data Files/OTM Test Data/OTM Order data.xlsx
+++ b/Data Files/OTM Test Data/OTM Order data.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>Order ID</t>
   </si>
@@ -124,6 +124,9 @@
   </si>
   <si>
     <t>SO_TEST456240</t>
+  </si>
+  <si>
+    <t>SO_TEST456846</t>
   </si>
 </sst>
 </file>
@@ -476,7 +479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87F71A60-031B-47A6-9564-1B4B3385F003}">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="15.51953125" collapsed="true"/>
@@ -645,6 +648,11 @@
     <row r="33">
       <c r="A33" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
